--- a/v1/dashboard_hanh_dong_v1.xlsx
+++ b/v1/dashboard_hanh_dong_v1.xlsx
@@ -16,9 +16,9 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Metrics'!$A$1:$J$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Workflow'!$A$1:$F$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Workflow'!$A$1:$F$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Roadmap_30_60_90'!$A$1:$F$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Evidence'!$A$1:$E$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Evidence'!$A$1:$E$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Change_Log'!$A$1:$D$2</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -879,7 +879,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -903,7 +903,7 @@
       </c>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>TO-BE sau chẩn đoán</t>
+          <t>TO-BE</t>
         </is>
       </c>
       <c r="D1" s="3" t="inlineStr">
@@ -928,17 +928,17 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>System Admin upload và gán asset</t>
+          <t>Upload và gán asset</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>Kiểm tra provenance, quyền lưu và readiness trước khi gán</t>
+          <t>Kiểm tra file rồi gán camera</t>
         </is>
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>System Admin</t>
+          <t>Nhóm dự án</t>
         </is>
       </c>
       <c r="E2" s="4" t="inlineStr">
@@ -948,7 +948,7 @@
       </c>
       <c r="F2" s="4" t="inlineStr">
         <is>
-          <t>Media private; decode validation</t>
+          <t>Decode validation</t>
         </is>
       </c>
     </row>
@@ -958,27 +958,27 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>Safety Manager cấu hình PPE/vùng</t>
+          <t>Cấu hình PPE/vùng</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>Rule có owner, version, severity và escalation policy</t>
+          <t>Lưu rule cho camera</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>Safety Manager</t>
+          <t>Nhóm dự án</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>AI áp rule deterministic</t>
+          <t>AI áp rule</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>Zone revision; role authorization</t>
+          <t>Authorization cơ bản</t>
         </is>
       </c>
     </row>
@@ -988,27 +988,27 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>AI detect/track và mở candidate</t>
+          <t>AI detect/track</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>Ghi freshness, latency, model version; fail-closed khi lỗi</t>
+          <t>Tạo cảnh báo khi rule khớp</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>Vision + Platform Owner</t>
+          <t>Chưa xác định rõ</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>AI tự động quan sát, không kết luận cuối</t>
+          <t>AI phát hiện và cảnh báo</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>Debounce; dedup; health gate</t>
+          <t>Debounce và dedup</t>
         </is>
       </c>
     </row>
@@ -1018,62 +1018,32 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>HITL xác nhận đúng/báo sai</t>
+          <t>Người dùng review</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Thêm SLA review, reason code và queue escalation</t>
+          <t>Xác nhận đúng hoặc báo sai</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>Safety Manager</t>
+          <t>Chưa có SLA/owner</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>AI trình bằng chứng đã làm mờ</t>
+          <t>AI trình snapshot</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>Privacy fail-closed; immutable audit</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>Area Manager xử lý event</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>Theo dõi time-to-resolve và owner theo camera/khu vực</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>Area Manager</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>AI tóm tắt chỉ mang tính hỗ trợ</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>Area-scoped authorization</t>
+          <t>Chưa có stop/escalation gate</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F6"/>
+  <autoFilter ref="A1:F5"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1135,27 +1105,27 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Tạo baseline đáng tin</t>
+          <t>Hoàn thiện chức năng</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>Chốt provenance; ground truth US-13; browser UAT; xử lý 14 failure</t>
+          <t>Sửa lỗi và chạy thêm test</t>
         </is>
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>Vision Lead + QA Lead</t>
+          <t>Nhóm dự án</t>
         </is>
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>≥200 scenario có nhãn; 0 blocker Sev-1/2</t>
+          <t>Test chức năng pass</t>
         </is>
       </c>
       <c r="F2" s="4" t="inlineStr">
         <is>
-          <t>Chưa qua thì không pilot</t>
+          <t>Chưa định nghĩa</t>
         </is>
       </c>
     </row>
@@ -1167,27 +1137,27 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>Pilot hẹp có HITL</t>
+          <t>Chạy thử</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>Một khu vực/một ca; đo precision, recall, false alarm, review SLA</t>
+          <t>Tăng số video demo</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>Safety Manager + Product Owner</t>
+          <t>Nhóm dự án</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>Precision ≥85%; critical recall ≥95%; review SLA ≥90%</t>
+          <t>Có thêm cảnh báo</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>Đạt 2 tuần liên tiếp</t>
+          <t>Chưa định nghĩa</t>
         </is>
       </c>
     </row>
@@ -1199,27 +1169,27 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>Mở rộng có điều kiện</t>
+          <t>Mở rộng</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>Soak 4 camera/30 phút; privacy audit; escalation/rollback drill</t>
+          <t>Chạy thêm camera</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>AI Governance Lead</t>
+          <t>Nhóm dự án</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>P95 alert ≤2s; 0 privacy incident; capacity report</t>
+          <t>Hệ thống tiếp tục hoạt động</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>Tiếp tục/sửa/dừng</t>
+          <t>Chưa định nghĩa</t>
         </is>
       </c>
     </row>
@@ -1235,7 +1205,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="33" customWidth="1" min="1" max="1"/>
@@ -1275,7 +1245,7 @@
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>Manual UI 01/09/2026</t>
+          <t>Manual UI</t>
         </is>
       </c>
       <c r="B2" s="4" t="inlineStr">
@@ -1290,19 +1260,19 @@
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>Luồng PPE, zone, HITL/privacy, auth, reconnect hoạt động</t>
+          <t>Sản phẩm đã sẵn sàng chạy thử</t>
         </is>
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>Không chứng minh accuracy nhà máy</t>
+          <t>Chưa tách giới hạn functional test</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>Focused backend 071c575</t>
+          <t>Focused backend</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
@@ -1312,103 +1282,49 @@
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>11/11 PASS trong 3,03s</t>
+          <t>11/11 PASS</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>Zone threshold, privacy fail-closed, idempotency, authorization</t>
+          <t>Các kiểm soát chính hoạt động</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>Không đại diện full suite</t>
+          <t>Chưa đối chiếu full quality gate</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>Quality gate rộng</t>
+          <t>Operational log</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>318 backend/vision</t>
+          <t>12.292 record</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>304 pass, 14 fail đã biết</t>
+          <t>1.544 inference completed</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>Repo còn nợ chất lượng cần xử lý/phân loại</t>
+          <t>Hệ thống được sử dụng</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>Không được báo toàn repo xanh</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>Operational JSONL</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>12.292 record</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>1.544 completed; 430 failed; 834 dropped; P95 1.306ms</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>Baseline kỹ thuật dev/test</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>Không phải production KPI</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>Local safety_events.db</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>0 event</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>Chưa có outcome HITL đủ mẫu</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>Baseline product hiện chưa đo</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>Không bịa precision/false alarm</t>
+          <t>Đang coi activity là giá trị</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E6"/>
+  <autoFilter ref="A1:E4"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
